--- a/六元_作品时间轴.xlsx
+++ b/六元_作品时间轴.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python练习\六元\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E763E6E9-2F9E-4C0C-978E-F7E067E4C2AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB20D277-340E-4D85-A039-BB49841B239E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{7D1B2066-D2B7-4F32-9662-CD01F844A157}"/>
   </bookViews>

--- a/六元_作品时间轴.xlsx
+++ b/六元_作品时间轴.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python练习\六元\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB20D277-340E-4D85-A039-BB49841B239E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946567E5-5819-4239-9AED-04B8D2E9D590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{7D1B2066-D2B7-4F32-9662-CD01F844A157}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7D1B2066-D2B7-4F32-9662-CD01F844A157}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$25</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="177">
   <si>
     <t>作品</t>
   </si>
@@ -278,10 +278,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>logo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>背景图</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -350,10 +346,6 @@
   </si>
   <si>
     <t>D:\python练习\六元\海岛舒服日志.jpg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>D:\python练习\六元\南京照相馆_logo.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -729,7 +721,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -740,9 +732,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48EAED5F-13BD-4F55-BCB4-40D0EB8C1A97}">
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="11.1328125" customWidth="1"/>
@@ -1087,16 +1076,15 @@
     <col min="3" max="3" width="11.6640625" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" customWidth="1"/>
     <col min="7" max="7" width="24.3984375" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" customWidth="1"/>
-    <col min="9" max="9" width="35.73046875" customWidth="1"/>
-    <col min="10" max="10" width="22.6640625" customWidth="1"/>
-    <col min="11" max="11" width="23.6640625" customWidth="1"/>
-    <col min="12" max="12" width="22.86328125" customWidth="1"/>
-    <col min="15" max="15" width="12.33203125" customWidth="1"/>
-    <col min="16" max="17" width="14.53125" customWidth="1"/>
+    <col min="8" max="8" width="35.73046875" customWidth="1"/>
+    <col min="9" max="9" width="22.6640625" customWidth="1"/>
+    <col min="10" max="10" width="23.6640625" customWidth="1"/>
+    <col min="11" max="11" width="22.86328125" customWidth="1"/>
+    <col min="14" max="14" width="12.33203125" customWidth="1"/>
+    <col min="15" max="16" width="14.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1122,19 +1110,16 @@
         <v>65</v>
       </c>
       <c r="I1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="J1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K1" t="s">
-        <v>62</v>
-      </c>
-      <c r="L1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1154,28 +1139,25 @@
         <v>20</v>
       </c>
       <c r="G2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="H2" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="I2" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
       <c r="J2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K2" t="s">
         <v>93</v>
       </c>
-      <c r="K2" t="s">
-        <v>94</v>
-      </c>
-      <c r="L2" t="s">
-        <v>95</v>
-      </c>
+      <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1195,28 +1177,25 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="H3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="I3" t="s">
-        <v>85</v>
+        <v>172</v>
       </c>
       <c r="J3" t="s">
+        <v>173</v>
+      </c>
+      <c r="K3" t="s">
         <v>174</v>
       </c>
-      <c r="K3" t="s">
-        <v>175</v>
-      </c>
-      <c r="L3" t="s">
-        <v>176</v>
-      </c>
+      <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1236,28 +1215,25 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H4" t="s">
         <v>84</v>
       </c>
       <c r="I4" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K4" t="s">
         <v>96</v>
       </c>
-      <c r="K4" t="s">
-        <v>97</v>
-      </c>
-      <c r="L4" t="s">
-        <v>98</v>
-      </c>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1277,28 +1253,25 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="J5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K5" t="s">
         <v>99</v>
       </c>
-      <c r="L5" t="s">
-        <v>101</v>
-      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1318,28 +1291,25 @@
         <v>25</v>
       </c>
       <c r="G6" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="I6" t="s">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="J6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K6" t="s">
         <v>102</v>
       </c>
-      <c r="K6" t="s">
-        <v>103</v>
-      </c>
-      <c r="L6" t="s">
-        <v>104</v>
-      </c>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
       <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A7" s="3" t="s">
         <v>26</v>
       </c>
@@ -1359,28 +1329,25 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H7" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="I7" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="J7" t="s">
+        <v>104</v>
+      </c>
+      <c r="K7" t="s">
         <v>105</v>
       </c>
-      <c r="K7" t="s">
-        <v>106</v>
-      </c>
-      <c r="L7" t="s">
-        <v>107</v>
-      </c>
+      <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -1400,28 +1367,25 @@
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="I8" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="J8" t="s">
+        <v>107</v>
+      </c>
+      <c r="K8" t="s">
         <v>108</v>
       </c>
-      <c r="K8" t="s">
-        <v>109</v>
-      </c>
-      <c r="L8" t="s">
-        <v>110</v>
-      </c>
+      <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -1440,29 +1404,26 @@
       <c r="F9" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>173</v>
+      <c r="G9" t="s">
+        <v>171</v>
       </c>
       <c r="H9" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="I9" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="J9" t="s">
+        <v>110</v>
+      </c>
+      <c r="K9" t="s">
         <v>111</v>
       </c>
-      <c r="K9" t="s">
-        <v>112</v>
-      </c>
-      <c r="L9" t="s">
-        <v>113</v>
-      </c>
+      <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1481,29 +1442,26 @@
       <c r="F10" t="s">
         <v>33</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>172</v>
+      <c r="G10" t="s">
+        <v>170</v>
       </c>
       <c r="H10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="J10" t="s">
+        <v>113</v>
+      </c>
+      <c r="K10" t="s">
         <v>114</v>
       </c>
-      <c r="K10" t="s">
-        <v>115</v>
-      </c>
-      <c r="L10" t="s">
-        <v>116</v>
-      </c>
+      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -1523,28 +1481,25 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H11" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="I11" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="J11" t="s">
+        <v>116</v>
+      </c>
+      <c r="K11" t="s">
         <v>117</v>
       </c>
-      <c r="K11" t="s">
-        <v>118</v>
-      </c>
-      <c r="L11" t="s">
-        <v>119</v>
-      </c>
+      <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
         <v>34</v>
       </c>
@@ -1564,28 +1519,25 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H12" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="I12" t="s">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="J12" t="s">
+        <v>119</v>
+      </c>
+      <c r="K12" t="s">
         <v>120</v>
       </c>
-      <c r="K12" t="s">
-        <v>121</v>
-      </c>
-      <c r="L12" t="s">
-        <v>122</v>
-      </c>
+      <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1605,28 +1557,25 @@
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="J13" t="s">
+        <v>122</v>
+      </c>
+      <c r="K13" t="s">
         <v>123</v>
       </c>
-      <c r="K13" t="s">
-        <v>124</v>
-      </c>
-      <c r="L13" t="s">
-        <v>125</v>
-      </c>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1646,28 +1595,25 @@
         <v>41</v>
       </c>
       <c r="G14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="J14" t="s">
+        <v>125</v>
+      </c>
+      <c r="K14" t="s">
         <v>126</v>
       </c>
-      <c r="K14" t="s">
-        <v>127</v>
-      </c>
-      <c r="L14" t="s">
-        <v>128</v>
-      </c>
+      <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>1921</v>
       </c>
@@ -1687,28 +1633,25 @@
         <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H15" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="I15" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="J15" t="s">
+        <v>128</v>
+      </c>
+      <c r="K15" t="s">
         <v>129</v>
       </c>
-      <c r="K15" t="s">
-        <v>130</v>
-      </c>
-      <c r="L15" t="s">
-        <v>131</v>
-      </c>
+      <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-    </row>
-    <row r="16" spans="1:18" ht="27.75" x14ac:dyDescent="0.4">
+    </row>
+    <row r="16" spans="1:17" ht="27.75" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1728,28 +1671,25 @@
         <v>46</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H16" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="I16" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="J16" t="s">
+        <v>131</v>
+      </c>
+      <c r="K16" t="s">
         <v>132</v>
       </c>
-      <c r="K16" t="s">
-        <v>133</v>
-      </c>
-      <c r="L16" t="s">
-        <v>134</v>
-      </c>
+      <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1769,28 +1709,25 @@
         <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="J17" t="s">
+        <v>134</v>
+      </c>
+      <c r="K17" t="s">
         <v>135</v>
       </c>
-      <c r="K17" t="s">
-        <v>136</v>
-      </c>
-      <c r="L17" t="s">
-        <v>137</v>
-      </c>
+      <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -1810,28 +1747,25 @@
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H18" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I18" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="J18" t="s">
+        <v>137</v>
+      </c>
+      <c r="K18" t="s">
         <v>138</v>
       </c>
-      <c r="K18" t="s">
-        <v>139</v>
-      </c>
-      <c r="L18" t="s">
-        <v>140</v>
-      </c>
+      <c r="O18" s="1"/>
       <c r="P18" s="1"/>
       <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1851,28 +1785,25 @@
         <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I19" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="J19" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" t="s">
         <v>141</v>
       </c>
-      <c r="K19" t="s">
-        <v>142</v>
-      </c>
-      <c r="L19" t="s">
-        <v>143</v>
-      </c>
+      <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1892,28 +1823,25 @@
         <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H20" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="I20" t="s">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="J20" t="s">
+        <v>143</v>
+      </c>
+      <c r="K20" t="s">
         <v>144</v>
       </c>
-      <c r="K20" t="s">
-        <v>145</v>
-      </c>
-      <c r="L20" t="s">
-        <v>146</v>
-      </c>
+      <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>43</v>
       </c>
@@ -1933,28 +1861,25 @@
         <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H21" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="J21" t="s">
+        <v>146</v>
+      </c>
+      <c r="K21" t="s">
         <v>147</v>
       </c>
-      <c r="K21" t="s">
-        <v>148</v>
-      </c>
-      <c r="L21" t="s">
-        <v>149</v>
-      </c>
+      <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>48</v>
       </c>
@@ -1974,28 +1899,25 @@
         <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J22" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K22" t="s">
         <v>99</v>
       </c>
-      <c r="L22" t="s">
-        <v>101</v>
-      </c>
+      <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>54</v>
       </c>
@@ -2015,25 +1937,22 @@
         <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J23" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K23" t="s">
-        <v>90</v>
-      </c>
-      <c r="L23" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>55</v>
       </c>
@@ -2053,25 +1972,22 @@
         <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H24" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I24" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="J24" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="K24" t="s">
         <v>99</v>
       </c>
-      <c r="L24" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.4">
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A25" s="3" t="s">
         <v>56</v>
       </c>
@@ -2091,22 +2007,19 @@
         <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H25" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I25" t="s">
-        <v>91</v>
+        <v>148</v>
       </c>
       <c r="J25" t="s">
+        <v>149</v>
+      </c>
+      <c r="K25" t="s">
         <v>150</v>
-      </c>
-      <c r="K25" t="s">
-        <v>151</v>
-      </c>
-      <c r="L25" t="s">
-        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/六元_作品时间轴.xlsx
+++ b/六元_作品时间轴.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python练习\六元\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946567E5-5819-4239-9AED-04B8D2E9D590}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED2C0EA-A279-42CD-AF40-21A5A2FDBE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7D1B2066-D2B7-4F32-9662-CD01F844A157}"/>
   </bookViews>
@@ -575,10 +575,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我想完成一次…完美的犯罪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>你神性的举动，却暴露了你兽性的行踪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -591,10 +587,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>我不是那个身体…已经很久了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>流水不争先，争的是滔滔不绝！</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -603,19 +595,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>这是我的国家，好美啊…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>你应该…轻轻地给油…
-傻子才会陷进去！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>我要回家！</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>......</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -664,11 +643,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>平安夜那天晚上我去了，我等了你一个晚上…</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>实现共产主义的最高原则是要建立一个无产阶级专政！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>很快的，人一下子就长大了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>平安夜那天晚上我去了，我等了你一个晚上...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>这是我的国家，好美啊...</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>做好了就会...像没做一样</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我不是那个身体...已经很久了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>我想完成一次...完美的犯罪</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -721,15 +720,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
@@ -1177,19 +1173,19 @@
         <v>8</v>
       </c>
       <c r="G3" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="H3" t="s">
         <v>83</v>
       </c>
       <c r="I3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="K3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
@@ -1215,7 +1211,7 @@
         <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H4" t="s">
         <v>84</v>
@@ -1234,7 +1230,7 @@
       <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B5" s="1">
@@ -1253,7 +1249,7 @@
         <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H5" t="s">
         <v>85</v>
@@ -1310,7 +1306,7 @@
       <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="1">
@@ -1329,7 +1325,7 @@
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="H7" t="s">
         <v>69</v>
@@ -1367,7 +1363,7 @@
         <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H8" t="s">
         <v>86</v>
@@ -1405,7 +1401,7 @@
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H9" t="s">
         <v>70</v>
@@ -1443,7 +1439,7 @@
         <v>33</v>
       </c>
       <c r="G10" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H10" t="s">
         <v>87</v>
@@ -1481,7 +1477,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H11" t="s">
         <v>71</v>
@@ -1500,7 +1496,7 @@
       <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="1">
@@ -1519,7 +1515,7 @@
         <v>36</v>
       </c>
       <c r="G12" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="H12" t="s">
         <v>72</v>
@@ -1557,7 +1553,7 @@
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H13" t="s">
         <v>73</v>
@@ -1633,7 +1629,7 @@
         <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H15" t="s">
         <v>75</v>
@@ -1651,7 +1647,7 @@
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" ht="27.75" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1670,8 +1666,8 @@
       <c r="F16" t="s">
         <v>46</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>161</v>
+      <c r="G16" t="s">
+        <v>174</v>
       </c>
       <c r="H16" t="s">
         <v>76</v>
@@ -1709,7 +1705,7 @@
         <v>64</v>
       </c>
       <c r="G17" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="H17" t="s">
         <v>77</v>
@@ -1747,7 +1743,7 @@
         <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="H18" t="s">
         <v>78</v>
@@ -1785,7 +1781,7 @@
         <v>51</v>
       </c>
       <c r="G19" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H19" t="s">
         <v>79</v>
@@ -1823,7 +1819,7 @@
         <v>53</v>
       </c>
       <c r="G20" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H20" t="s">
         <v>66</v>
@@ -1861,7 +1857,7 @@
         <v>44</v>
       </c>
       <c r="G21" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H21" t="s">
         <v>80</v>
@@ -1899,7 +1895,7 @@
         <v>49</v>
       </c>
       <c r="G22" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H22" t="s">
         <v>81</v>
@@ -1937,7 +1933,7 @@
         <v>59</v>
       </c>
       <c r="G23" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H23" t="s">
         <v>88</v>
@@ -1972,7 +1968,7 @@
         <v>58</v>
       </c>
       <c r="G24" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="H24" t="s">
         <v>82</v>
@@ -1988,7 +1984,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B25" s="1">
@@ -2007,7 +2003,7 @@
         <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="H25" t="s">
         <v>89</v>

--- a/六元_作品时间轴.xlsx
+++ b/六元_作品时间轴.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\python练习\六元\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED2C0EA-A279-42CD-AF40-21A5A2FDBE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD66ED5-E0F1-48DA-BBC5-C0A96D55F9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{7D1B2066-D2B7-4F32-9662-CD01F844A157}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="183">
   <si>
     <t>作品</t>
   </si>
@@ -668,6 +668,30 @@
   </si>
   <si>
     <t>我想完成一次...完美的犯罪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\海岛舒服日志_1.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\海岛舒服日志_2.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\海岛舒服日志_3.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\我的朋友安德烈_1.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\我的朋友安德烈_2.mp4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\python练习\六元\我的朋友安德烈_3.mp4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1901,13 +1925,13 @@
         <v>81</v>
       </c>
       <c r="I22" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="J22" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="K22" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -1974,13 +1998,13 @@
         <v>82</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>177</v>
       </c>
       <c r="J24" t="s">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="K24" t="s">
-        <v>99</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.4">
